--- a/workbooks/after-sales.xlsx
+++ b/workbooks/after-sales.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,45 +516,45 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>45345.19027777778</v>
+        <v>45509.38958333333</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5448788169564495</v>
+        <v>2434.15</v>
       </c>
       <c r="D2" t="n">
-        <v>3616.65739</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2000</v>
+        <v>2478.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>45327.97185185185</v>
+        <v>45345.19027777778</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HBAR</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.06803486902880881</v>
+        <v>0.5448788169564495</v>
       </c>
       <c r="D3" t="n">
-        <v>10.87677555</v>
+        <v>3616.65739</v>
       </c>
       <c r="E3" t="n">
-        <v>0.74</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>45320.48010416667</v>
+        <v>45327.97185185185</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -562,18 +562,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07333113036895253</v>
+        <v>0.06803486902880881</v>
       </c>
       <c r="D4" t="n">
-        <v>72.68400164000001</v>
+        <v>10.87677555</v>
       </c>
       <c r="E4" t="n">
-        <v>5.33</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>45281.83146990741</v>
+        <v>45320.48010416667</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -581,18 +581,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.08702114026711345</v>
+        <v>0.07333113036895253</v>
       </c>
       <c r="D5" t="n">
-        <v>34.12963782</v>
+        <v>72.68400164000001</v>
       </c>
       <c r="E5" t="n">
-        <v>2.97</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>45266.91903935185</v>
+        <v>45281.83146990741</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -600,18 +600,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.06583444599568089</v>
+        <v>0.08702114026711345</v>
       </c>
       <c r="D6" t="n">
-        <v>48.30298109</v>
+        <v>34.12963782</v>
       </c>
       <c r="E6" t="n">
-        <v>3.18</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>45247.9331712963</v>
+        <v>45266.91903935185</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -619,18 +619,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.06109126144076911</v>
+        <v>0.06583444599568089</v>
       </c>
       <c r="D7" t="n">
-        <v>10.96719865</v>
+        <v>48.30298109</v>
       </c>
       <c r="E7" t="n">
-        <v>0.67</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>45243.92203703704</v>
+        <v>45247.9331712963</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -638,56 +638,56 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.06220576971199036</v>
+        <v>0.06109126144076911</v>
       </c>
       <c r="D8" t="n">
-        <v>55.78260692</v>
+        <v>10.96719865</v>
       </c>
       <c r="E8" t="n">
-        <v>3.47</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>45230.47232638889</v>
+        <v>45243.92203703704</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>USDC</t>
+          <t>HBAR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.00028758268002</v>
+        <v>0.06220576971199036</v>
       </c>
       <c r="D9" t="n">
-        <v>0.159954</v>
+        <v>55.78260692</v>
       </c>
       <c r="E9" t="n">
-        <v>0.16</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>45224.69118055556</v>
+        <v>45230.47232638889</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HBAR</t>
+          <t>USDC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.05164678344993132</v>
+        <v>1.00028758268002</v>
       </c>
       <c r="D10" t="n">
-        <v>15.68345492</v>
+        <v>0.159954</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>45219.75883101852</v>
+        <v>45224.69118055556</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -695,18 +695,18 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.04581990110018071</v>
+        <v>0.05164678344993132</v>
       </c>
       <c r="D11" t="n">
-        <v>297.4689965</v>
+        <v>15.68345492</v>
       </c>
       <c r="E11" t="n">
-        <v>13.63</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>45146.03603009259</v>
+        <v>45219.75883101852</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -714,18 +714,18 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.05645797071004285</v>
+        <v>0.04581990110018071</v>
       </c>
       <c r="D12" t="n">
-        <v>470.261323</v>
+        <v>297.4689965</v>
       </c>
       <c r="E12" t="n">
-        <v>26.55</v>
+        <v>13.63</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>45146.03285879629</v>
+        <v>45146.03603009259</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -733,18 +733,18 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0584899292712627</v>
+        <v>0.05645797071004285</v>
       </c>
       <c r="D13" t="n">
-        <v>43834.38366132</v>
+        <v>470.261323</v>
       </c>
       <c r="E13" t="n">
-        <v>2563.87</v>
+        <v>26.55</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>45146.03059027778</v>
+        <v>45146.03285879629</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -752,37 +752,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.05909090908667258</v>
+        <v>0.0584899292712627</v>
       </c>
       <c r="D14" t="n">
-        <v>53.64615385</v>
+        <v>43834.38366132</v>
       </c>
       <c r="E14" t="n">
-        <v>3.17</v>
+        <v>2563.87</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>45131.44159722222</v>
+        <v>45146.03059027778</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>HBAR</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.704848484832252</v>
+        <v>0.05909090908667258</v>
       </c>
       <c r="D15" t="n">
-        <v>1418.744626</v>
+        <v>53.64615385</v>
       </c>
       <c r="E15" t="n">
-        <v>1000</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>45124.80702546296</v>
+        <v>45131.44159722222</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -790,18 +790,18 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.7312994935923857</v>
+        <v>0.704848484832252</v>
       </c>
       <c r="D16" t="n">
-        <v>922.768313</v>
+        <v>1418.744626</v>
       </c>
       <c r="E16" t="n">
-        <v>674.8200000000001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>45124.77539351852</v>
+        <v>45124.80702546296</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -809,18 +809,18 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.7241962123126896</v>
+        <v>0.7312994935923857</v>
       </c>
       <c r="D17" t="n">
-        <v>941.043309</v>
+        <v>922.768313</v>
       </c>
       <c r="E17" t="n">
-        <v>681.5</v>
+        <v>674.8200000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>45124.75659722222</v>
+        <v>45124.77539351852</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -828,37 +828,37 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.7469625014359766</v>
+        <v>0.7241962123126896</v>
       </c>
       <c r="D18" t="n">
-        <v>971.856015</v>
+        <v>941.043309</v>
       </c>
       <c r="E18" t="n">
-        <v>725.9400000000001</v>
+        <v>681.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>45087.11783564815</v>
+        <v>45124.75659722222</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HBAR</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0484474033023344</v>
+        <v>0.7469625014359766</v>
       </c>
       <c r="D19" t="n">
-        <v>130.2443386</v>
+        <v>971.856015</v>
       </c>
       <c r="E19" t="n">
-        <v>6.31</v>
+        <v>725.9400000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>45067.3153125</v>
+        <v>45087.11783564815</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -866,18 +866,18 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.05301888793675442</v>
+        <v>0.0484474033023344</v>
       </c>
       <c r="D20" t="n">
-        <v>58.46972882</v>
+        <v>130.2443386</v>
       </c>
       <c r="E20" t="n">
-        <v>3.1</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>45058.33905092593</v>
+        <v>45067.3153125</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -885,37 +885,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0513950184195149</v>
+        <v>0.05301888793675442</v>
       </c>
       <c r="D21" t="n">
-        <v>283.8796531</v>
+        <v>58.46972882</v>
       </c>
       <c r="E21" t="n">
-        <v>14.59</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>45058.19652777778</v>
+        <v>45058.33905092593</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>HBAR</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.428976624570404</v>
+        <v>0.0513950184195149</v>
       </c>
       <c r="D22" t="n">
-        <v>44.590986</v>
+        <v>283.8796531</v>
       </c>
       <c r="E22" t="n">
-        <v>19.13</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>45054.77490740741</v>
+        <v>45058.19652777778</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -923,56 +923,56 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.4503605885935721</v>
+        <v>0.428976624570404</v>
       </c>
       <c r="D23" t="n">
-        <v>113.287</v>
+        <v>44.590986</v>
       </c>
       <c r="E23" t="n">
-        <v>51.02</v>
+        <v>19.13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>45014.81280092592</v>
+        <v>45054.77490740741</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HBAR</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.05890923103526676</v>
+        <v>0.4503605885935721</v>
       </c>
       <c r="D24" t="n">
-        <v>6.45060194</v>
+        <v>113.287</v>
       </c>
       <c r="E24" t="n">
-        <v>0.38</v>
+        <v>51.02</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>45013.15342592593</v>
+        <v>45014.81280092592</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>XRP</t>
+          <t>HBAR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.4801375295817313</v>
+        <v>0.05890923103526676</v>
       </c>
       <c r="D25" t="n">
-        <v>2066.699516</v>
+        <v>6.45060194</v>
       </c>
       <c r="E25" t="n">
-        <v>992.3</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>45012.1265162037</v>
+        <v>45013.15342592593</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -980,18 +980,18 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.4488356714405042</v>
+        <v>0.4801375295817313</v>
       </c>
       <c r="D26" t="n">
-        <v>805.484107</v>
+        <v>2066.699516</v>
       </c>
       <c r="E26" t="n">
-        <v>361.53</v>
+        <v>992.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>45010.50967592592</v>
+        <v>45012.1265162037</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -999,18 +999,18 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.4546727091699747</v>
+        <v>0.4488356714405042</v>
       </c>
       <c r="D27" t="n">
-        <v>219.938426</v>
+        <v>805.484107</v>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>361.53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>45006.65659722222</v>
+        <v>45010.50967592592</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1018,37 +1018,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.4371946406745632</v>
+        <v>0.4546727091699747</v>
       </c>
       <c r="D28" t="n">
-        <v>1152.377951</v>
+        <v>219.938426</v>
       </c>
       <c r="E28" t="n">
-        <v>503.82</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>45005.71923611111</v>
+        <v>45006.65659722222</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HBAR</t>
+          <t>XRP</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.06300502512508706</v>
+        <v>0.4371946406745632</v>
       </c>
       <c r="D29" t="n">
-        <v>317.43499761</v>
+        <v>1152.377951</v>
       </c>
       <c r="E29" t="n">
-        <v>20</v>
+        <v>503.82</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>44998.83645833333</v>
+        <v>45005.71923611111</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.06458291457213151</v>
+        <v>0.06300502512508706</v>
       </c>
       <c r="D30" t="n">
-        <v>309.67942733</v>
+        <v>317.43499761</v>
       </c>
       <c r="E30" t="n">
         <v>20</v>
@@ -1067,7 +1067,7 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>44995.76827546296</v>
+        <v>44998.83645833333</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1075,18 +1075,18 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.05924242424243397</v>
+        <v>0.06458291457213151</v>
       </c>
       <c r="D31" t="n">
-        <v>10127.87723785</v>
+        <v>309.67942733</v>
       </c>
       <c r="E31" t="n">
-        <v>600</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>44991.70733796297</v>
+        <v>44995.76827546296</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1094,18 +1094,18 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.06411055276443217</v>
+        <v>0.05924242424243397</v>
       </c>
       <c r="D32" t="n">
-        <v>311.96112243</v>
+        <v>10127.87723785</v>
       </c>
       <c r="E32" t="n">
-        <v>20</v>
+        <v>600</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>44987.0953125</v>
+        <v>44991.70733796297</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1113,18 +1113,18 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0690242930183286</v>
+        <v>0.06411055276443217</v>
       </c>
       <c r="D33" t="n">
-        <v>12639.46303323</v>
+        <v>311.96112243</v>
       </c>
       <c r="E33" t="n">
-        <v>872.4299999999999</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>44984.69497685185</v>
+        <v>44987.0953125</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1132,18 +1132,18 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.07290452261403836</v>
+        <v>0.0690242930183286</v>
       </c>
       <c r="D34" t="n">
-        <v>274.33140336</v>
+        <v>12639.46303323</v>
       </c>
       <c r="E34" t="n">
-        <v>20</v>
+        <v>872.4299999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>44963.71480324074</v>
+        <v>44984.69497685185</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.07010918921294899</v>
+        <v>0.07290452261403836</v>
       </c>
       <c r="D35" t="n">
-        <v>264.01674599</v>
+        <v>274.33140336</v>
       </c>
       <c r="E35" t="n">
         <v>20</v>
@@ -1162,7 +1162,7 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>44956.84309027778</v>
+        <v>44963.71480324074</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.06417085427117038</v>
+        <v>0.07010918921294899</v>
       </c>
       <c r="D36" t="n">
-        <v>288.44870791</v>
+        <v>264.01674599</v>
       </c>
       <c r="E36" t="n">
         <v>20</v>
@@ -1181,7 +1181,7 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>44949.78057870371</v>
+        <v>44956.84309027778</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.06974874371841119</v>
+        <v>0.06417085427117038</v>
       </c>
       <c r="D37" t="n">
-        <v>265.38112392</v>
+        <v>288.44870791</v>
       </c>
       <c r="E37" t="n">
         <v>20</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>44946.91366898148</v>
+        <v>44949.78057870371</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1208,18 +1208,18 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.07608365565557711</v>
+        <v>0.06974874371841119</v>
       </c>
       <c r="D38" t="n">
-        <v>6661.40079847</v>
+        <v>265.38112392</v>
       </c>
       <c r="E38" t="n">
-        <v>506.82</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>44942.81034722222</v>
+        <v>44946.91366898148</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1227,18 +1227,18 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.05367839196031339</v>
+        <v>0.07608365565557711</v>
       </c>
       <c r="D39" t="n">
-        <v>372.58940273</v>
+        <v>6661.40079847</v>
       </c>
       <c r="E39" t="n">
-        <v>20</v>
+        <v>506.82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>44937.76524305555</v>
+        <v>44942.81034722222</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1246,18 +1246,18 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.04459995351554337</v>
+        <v>0.05367839196031339</v>
       </c>
       <c r="D40" t="n">
-        <v>872.76773121</v>
+        <v>372.58940273</v>
       </c>
       <c r="E40" t="n">
-        <v>38.93</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>44937.76501157408</v>
+        <v>44937.76524305555</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1265,18 +1265,18 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.04459144923770082</v>
+        <v>0.04459995351554337</v>
       </c>
       <c r="D41" t="n">
-        <v>655.50684043</v>
+        <v>872.76773121</v>
       </c>
       <c r="E41" t="n">
-        <v>29.23</v>
+        <v>38.93</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>44937.76446759259</v>
+        <v>44937.76501157408</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1284,18 +1284,18 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.04455868101211714</v>
+        <v>0.04459144923770082</v>
       </c>
       <c r="D42" t="n">
-        <v>656.21331996</v>
+        <v>655.50684043</v>
       </c>
       <c r="E42" t="n">
-        <v>29.24</v>
+        <v>29.23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>44935.6687037037</v>
+        <v>44937.76446759259</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1303,69 +1303,88 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.04513567839200289</v>
+        <v>0.04455868101211714</v>
       </c>
       <c r="D43" t="n">
-        <v>443.1084391</v>
+        <v>656.21331996</v>
       </c>
       <c r="E43" t="n">
-        <v>20</v>
+        <v>29.24</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>44893.29744212963</v>
+        <v>44935.6687037037</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>HBAR</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1178.442052468954</v>
+        <v>0.04513567839200289</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0003157800000000016</v>
+        <v>443.1084391</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3499999999999979</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
-        <v>44867.11673611111</v>
+        <v>44893.29744212963</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HBAR</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.05807072647076265</v>
+        <v>1178.442052468954</v>
       </c>
       <c r="D45" t="n">
-        <v>839.14913695</v>
+        <v>0.0003157800000000016</v>
       </c>
       <c r="E45" t="n">
-        <v>48.73</v>
+        <v>0.3499999999999979</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
+        <v>44867.11673611111</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HBAR</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.05807072647076265</v>
+      </c>
+      <c r="D46" t="n">
+        <v>839.14913695</v>
+      </c>
+      <c r="E46" t="n">
+        <v>48.73</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
         <v>44867.11646990741</v>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>HBAR</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HBAR</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
         <v>0.05805059388054373</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D47" t="n">
         <v>839.61242671</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E47" t="n">
         <v>48.74</v>
       </c>
     </row>
